--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487122_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487122_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.3175</v>
+        <v>7.1127</v>
       </c>
       <c r="E2" t="n">
-        <v>4.8697</v>
+        <v>5.1295</v>
       </c>
       <c r="F2" t="n">
-        <v>1.4478</v>
+        <v>1.9832</v>
       </c>
       <c r="G2" t="n">
         <v>1.9413</v>
@@ -610,13 +610,13 @@
         <v>2.3161</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.5936</v>
+        <v>0.2016</v>
       </c>
       <c r="T2" t="n">
-        <v>0.2644</v>
+        <v>0.5242</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.858</v>
+        <v>-0.3226</v>
       </c>
       <c r="V2" t="n">
         <v>4.5838</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.4629</v>
+        <v>4.8728</v>
       </c>
       <c r="E3" t="n">
-        <v>1.4911</v>
+        <v>2.3924</v>
       </c>
       <c r="F3" t="n">
-        <v>1.9718</v>
+        <v>2.4804</v>
       </c>
       <c r="G3" t="n">
         <v>5.6547</v>
@@ -688,13 +688,13 @@
         <v>1.5441</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.4125</v>
+        <v>-0.0027</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.0113</v>
+        <v>-0.11</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.4013</v>
+        <v>0.1074</v>
       </c>
       <c r="V3" t="n">
         <v>0.5717</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. TOURE</t>
+          <t>A. MARTÍN CASTAÑEDA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.0461</v>
+        <v>2.6702</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4899</v>
+        <v>-0.5538999999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>2.5562</v>
+        <v>3.2241</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6673</v>
+        <v>1.8002</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0319</v>
+        <v>0.4679</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6355</v>
+        <v>1.3323</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.3885</v>
+        <v>-0.9447</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.3885</v>
+        <v>-1.1075</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>0.1628</v>
       </c>
       <c r="M4" t="n">
-        <v>1.0558</v>
+        <v>2.7449</v>
       </c>
       <c r="N4" t="n">
-        <v>0.4203</v>
+        <v>1.5754</v>
       </c>
       <c r="O4" t="n">
-        <v>0.6355</v>
+        <v>1.1695</v>
       </c>
       <c r="P4" t="n">
-        <v>0.193</v>
+        <v>-0.386</v>
       </c>
       <c r="Q4" t="n">
         <v>-0.965</v>
       </c>
       <c r="R4" t="n">
-        <v>1.158</v>
+        <v>0.579</v>
       </c>
       <c r="S4" t="n">
-        <v>1.5718</v>
+        <v>0.0281</v>
       </c>
       <c r="T4" t="n">
-        <v>1.2295</v>
+        <v>0.1279</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3423</v>
+        <v>-0.0999</v>
       </c>
       <c r="V4" t="n">
-        <v>0.614</v>
+        <v>1.228</v>
       </c>
       <c r="W4" t="n">
-        <v>0.614</v>
+        <v>1.228</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. VASQUEZ BAUTISTA</t>
+          <t>A. TOURE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.4876</v>
+        <v>2.3441</v>
       </c>
       <c r="E5" t="n">
-        <v>0.453</v>
+        <v>-0.0514</v>
       </c>
       <c r="F5" t="n">
-        <v>2.0346</v>
+        <v>2.3956</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.0633</v>
+        <v>0.6673</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.4574</v>
+        <v>0.0319</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3941</v>
+        <v>0.6355</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.4177</v>
+        <v>-0.3885</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.2317</v>
+        <v>-0.3885</v>
       </c>
       <c r="L5" t="n">
-        <v>0.8139999999999999</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3544</v>
+        <v>1.0558</v>
       </c>
       <c r="N5" t="n">
-        <v>0.7743</v>
+        <v>0.4203</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.4199</v>
+        <v>0.6355</v>
       </c>
       <c r="P5" t="n">
-        <v>0.772</v>
+        <v>0.193</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-0.965</v>
       </c>
       <c r="R5" t="n">
-        <v>0.772</v>
+        <v>1.158</v>
       </c>
       <c r="S5" t="n">
-        <v>3.0068</v>
+        <v>0.8698</v>
       </c>
       <c r="T5" t="n">
-        <v>1.5269</v>
+        <v>0.6881</v>
       </c>
       <c r="U5" t="n">
-        <v>1.4799</v>
+        <v>0.1817</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.228</v>
+        <v>0.614</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.6562</v>
+        <v>0.614</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.5717</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>V. TAVERAS RAFAEL</t>
+          <t>A. VASQUEZ BAUTISTA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.9448</v>
+        <v>0.6028</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.0471</v>
+        <v>-0.5485</v>
       </c>
       <c r="F6" t="n">
-        <v>3.992</v>
+        <v>1.1512</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.305</v>
+        <v>-0.0633</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.6459</v>
+        <v>-0.4574</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.6591</v>
+        <v>0.3941</v>
       </c>
       <c r="J6" t="n">
-        <v>-2.6663</v>
+        <v>-0.4177</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.3718</v>
+        <v>-1.2317</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.2945</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="M6" t="n">
-        <v>0.3614</v>
+        <v>0.3544</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.2741</v>
+        <v>0.7743</v>
       </c>
       <c r="O6" t="n">
-        <v>0.6355</v>
+        <v>-0.4199</v>
       </c>
       <c r="P6" t="n">
-        <v>-2.7021</v>
+        <v>0.772</v>
       </c>
       <c r="Q6" t="n">
-        <v>-4.8252</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.1231</v>
+        <v>0.772</v>
       </c>
       <c r="S6" t="n">
-        <v>4.4537</v>
+        <v>1.122</v>
       </c>
       <c r="T6" t="n">
-        <v>3.6024</v>
+        <v>0.5255</v>
       </c>
       <c r="U6" t="n">
-        <v>0.8512999999999999</v>
+        <v>0.5965</v>
       </c>
       <c r="V6" t="n">
-        <v>2.4982</v>
+        <v>-1.228</v>
       </c>
       <c r="W6" t="n">
-        <v>1.842</v>
+        <v>-0.6562</v>
       </c>
       <c r="X6" t="n">
-        <v>0.6562</v>
+        <v>-0.5717</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. MARTÍN CASTAÑEDA</t>
+          <t>D. CARRETERO GARCIA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.7154</v>
+        <v>0.2952</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.4551</v>
+        <v>-2.2023</v>
       </c>
       <c r="F7" t="n">
-        <v>3.1706</v>
+        <v>2.4976</v>
       </c>
       <c r="G7" t="n">
-        <v>1.8002</v>
+        <v>0.5021</v>
       </c>
       <c r="H7" t="n">
-        <v>0.4679</v>
+        <v>-0.5382</v>
       </c>
       <c r="I7" t="n">
-        <v>1.3323</v>
+        <v>1.0403</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.9447</v>
+        <v>-0.226</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.1075</v>
+        <v>-0.8851</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1628</v>
+        <v>0.6591</v>
       </c>
       <c r="M7" t="n">
-        <v>2.7449</v>
+        <v>0.7281</v>
       </c>
       <c r="N7" t="n">
-        <v>1.5754</v>
+        <v>0.3469</v>
       </c>
       <c r="O7" t="n">
-        <v>1.1695</v>
+        <v>0.3813</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.386</v>
+        <v>-0.579</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.965</v>
+        <v>-1.9301</v>
       </c>
       <c r="R7" t="n">
-        <v>0.579</v>
+        <v>1.3511</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.9267</v>
+        <v>0.0862</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.7733</v>
+        <v>-0.3321</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1534</v>
+        <v>0.4184</v>
       </c>
       <c r="V7" t="n">
-        <v>1.228</v>
+        <v>0.2859</v>
       </c>
       <c r="W7" t="n">
-        <v>1.228</v>
+        <v>0.2859</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>D. CARRETERO GARCIA</t>
+          <t>C. HERNÁNDEZ MARTÍN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.3661</v>
+        <v>0.0243</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.703</v>
+        <v>-0.1753</v>
       </c>
       <c r="F9" t="n">
-        <v>2.337</v>
+        <v>0.1996</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5021</v>
+        <v>0.3475</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.5382</v>
+        <v>1.0215</v>
       </c>
       <c r="I9" t="n">
-        <v>1.0403</v>
+        <v>-0.674</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.226</v>
+        <v>0.3674</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.8851</v>
+        <v>1.035</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6591</v>
+        <v>-0.6676</v>
       </c>
       <c r="M9" t="n">
-        <v>0.7281</v>
+        <v>-0.0199</v>
       </c>
       <c r="N9" t="n">
-        <v>0.3469</v>
+        <v>-0.0134</v>
       </c>
       <c r="O9" t="n">
-        <v>0.3813</v>
+        <v>-0.0064</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.579</v>
+        <v>-0.193</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.9301</v>
+        <v>-0.965</v>
       </c>
       <c r="R9" t="n">
-        <v>1.3511</v>
+        <v>0.772</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5750999999999999</v>
+        <v>0.1557</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.8328</v>
+        <v>0.4224</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2578</v>
+        <v>-0.2667</v>
       </c>
       <c r="V9" t="n">
-        <v>0.2859</v>
+        <v>-0.2859</v>
       </c>
       <c r="W9" t="n">
-        <v>0.2859</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.2859</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>C. HERNÁNDEZ MARTÍN</t>
+          <t>M. CARRETERO GARCÍA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.7163</v>
+        <v>-0.4182</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.8356</v>
+        <v>0.4066</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1193</v>
+        <v>-0.8247</v>
       </c>
       <c r="G10" t="n">
-        <v>0.3475</v>
+        <v>0.713</v>
       </c>
       <c r="H10" t="n">
-        <v>1.0215</v>
+        <v>1.4862</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.674</v>
+        <v>-0.7733</v>
       </c>
       <c r="J10" t="n">
-        <v>0.3674</v>
+        <v>0.3253</v>
       </c>
       <c r="K10" t="n">
-        <v>1.035</v>
+        <v>0.9522</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.6676</v>
+        <v>-0.6269</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.0199</v>
+        <v>0.3877</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.0134</v>
+        <v>0.5341</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.0064</v>
+        <v>-0.1464</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.193</v>
+        <v>0.193</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.965</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.772</v>
+        <v>0.193</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.585</v>
+        <v>-0.09619999999999999</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.238</v>
+        <v>0.0813</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.347</v>
+        <v>-0.1775</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.2859</v>
+        <v>-1.228</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.2859</v>
+        <v>-1.228</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. CARRETERO GARCÍA</t>
+          <t>V. TAVERAS RAFAEL</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.7523</v>
+        <v>-0.8343</v>
       </c>
       <c r="E11" t="n">
-        <v>0.2063</v>
+        <v>-4.2909</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.9586</v>
+        <v>3.4566</v>
       </c>
       <c r="G11" t="n">
-        <v>0.713</v>
+        <v>-2.305</v>
       </c>
       <c r="H11" t="n">
-        <v>1.4862</v>
+        <v>-1.6459</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.7733</v>
+        <v>-0.6591</v>
       </c>
       <c r="J11" t="n">
-        <v>0.3253</v>
+        <v>-2.6663</v>
       </c>
       <c r="K11" t="n">
-        <v>0.9522</v>
+        <v>-1.3718</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.6269</v>
+        <v>-1.2945</v>
       </c>
       <c r="M11" t="n">
-        <v>0.3877</v>
+        <v>0.3614</v>
       </c>
       <c r="N11" t="n">
-        <v>0.5341</v>
+        <v>-0.2741</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.1464</v>
+        <v>0.6355</v>
       </c>
       <c r="P11" t="n">
-        <v>0.193</v>
+        <v>-2.7021</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-4.8252</v>
       </c>
       <c r="R11" t="n">
-        <v>0.193</v>
+        <v>2.1231</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.4303</v>
+        <v>1.6746</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.119</v>
+        <v>1.3587</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3113</v>
+        <v>0.3159</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.228</v>
+        <v>2.4982</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.842</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.228</v>
+        <v>0.6562</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>M. SOLORZANO COLSA</t>
+          <t>A. RUIZ FERNÁNDEZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,58 +1345,58 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.9069</v>
+        <v>-1.5089</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.8979</v>
+        <v>-0.6232</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.009</v>
+        <v>-0.8857</v>
       </c>
       <c r="G12" t="n">
-        <v>2.7291</v>
+        <v>0.3685</v>
       </c>
       <c r="H12" t="n">
-        <v>1.9116</v>
+        <v>0.1014</v>
       </c>
       <c r="I12" t="n">
-        <v>0.8175</v>
+        <v>0.267</v>
       </c>
       <c r="J12" t="n">
-        <v>3.0085</v>
+        <v>0.0414</v>
       </c>
       <c r="K12" t="n">
-        <v>1.6248</v>
+        <v>0.0414</v>
       </c>
       <c r="L12" t="n">
-        <v>1.3838</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.2794</v>
+        <v>0.3271</v>
       </c>
       <c r="N12" t="n">
-        <v>0.2868</v>
+        <v>0.06</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.5662</v>
+        <v>0.267</v>
       </c>
       <c r="P12" t="n">
-        <v>-3.2811</v>
+        <v>-0.772</v>
       </c>
       <c r="Q12" t="n">
-        <v>-3.8602</v>
+        <v>-0.965</v>
       </c>
       <c r="R12" t="n">
-        <v>0.579</v>
+        <v>0.193</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.1269</v>
+        <v>0.1226</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.0462</v>
+        <v>0.3004</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.08069999999999999</v>
+        <v>-0.1778</v>
       </c>
       <c r="V12" t="n">
         <v>-1.228</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A. RUIZ FERNÁNDEZ</t>
+          <t>M. SOLORZANO COLSA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,58 +1423,58 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.9223</v>
+        <v>-1.5529</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.9831</v>
+        <v>-0.5974</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.9392</v>
+        <v>-0.9555</v>
       </c>
       <c r="G13" t="n">
-        <v>0.3685</v>
+        <v>2.7291</v>
       </c>
       <c r="H13" t="n">
-        <v>0.1014</v>
+        <v>1.9116</v>
       </c>
       <c r="I13" t="n">
-        <v>0.267</v>
+        <v>0.8175</v>
       </c>
       <c r="J13" t="n">
-        <v>0.0414</v>
+        <v>3.0085</v>
       </c>
       <c r="K13" t="n">
-        <v>0.0414</v>
+        <v>1.6248</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.3838</v>
       </c>
       <c r="M13" t="n">
-        <v>0.3271</v>
+        <v>-0.2794</v>
       </c>
       <c r="N13" t="n">
-        <v>0.06</v>
+        <v>0.2868</v>
       </c>
       <c r="O13" t="n">
-        <v>0.267</v>
+        <v>-0.5662</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.772</v>
+        <v>-3.2811</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.965</v>
+        <v>-3.8602</v>
       </c>
       <c r="R13" t="n">
-        <v>0.193</v>
+        <v>0.579</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.2908</v>
+        <v>0.227</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.0595</v>
+        <v>0.2542</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2313</v>
+        <v>-0.0271</v>
       </c>
       <c r="V13" t="n">
         <v>-1.228</v>
@@ -1501,25 +1501,25 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>13.4439</v>
+        <v>13.7413</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.411799999999999</v>
+        <v>-1.114399999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>14.856</v>
+        <v>14.8559</v>
       </c>
       <c r="G14" t="n">
         <v>12.4889</v>
       </c>
       <c r="H14" t="n">
-        <v>7.9122</v>
+        <v>7.912199999999999</v>
       </c>
       <c r="I14" t="n">
         <v>4.5766</v>
       </c>
       <c r="J14" t="n">
-        <v>3.134999999999999</v>
+        <v>3.135</v>
       </c>
       <c r="K14" t="n">
         <v>2.3066</v>
@@ -1528,13 +1528,13 @@
         <v>0.8284</v>
       </c>
       <c r="M14" t="n">
-        <v>9.354100000000001</v>
+        <v>9.354099999999999</v>
       </c>
       <c r="N14" t="n">
-        <v>5.605700000000001</v>
+        <v>5.6057</v>
       </c>
       <c r="O14" t="n">
-        <v>3.748499999999999</v>
+        <v>3.748500000000001</v>
       </c>
       <c r="P14" t="n">
         <v>-7.7203</v>
@@ -1546,16 +1546,16 @@
         <v>11.5804</v>
       </c>
       <c r="S14" t="n">
-        <v>4.0914</v>
+        <v>4.388700000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>3.5431</v>
+        <v>3.840599999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>0.5483</v>
+        <v>0.5483000000000001</v>
       </c>
       <c r="V14" t="n">
-        <v>4.5837</v>
+        <v>4.583700000000002</v>
       </c>
       <c r="W14" t="n">
         <v>11.211</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.4074</v>
+        <v>2.4817</v>
       </c>
       <c r="E15" t="n">
-        <v>0.6768</v>
+        <v>0.3764</v>
       </c>
       <c r="F15" t="n">
-        <v>1.7305</v>
+        <v>2.1053</v>
       </c>
       <c r="G15" t="n">
         <v>2.5879</v>
@@ -1624,13 +1624,13 @@
         <v>1.5441</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.8804</v>
+        <v>-0.8061</v>
       </c>
       <c r="T15" t="n">
-        <v>0.279</v>
+        <v>-0.0214</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.1594</v>
+        <v>-0.7846</v>
       </c>
       <c r="V15" t="n">
         <v>0.1208</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. URTXULUTEGI NAVARRI</t>
+          <t>U. PEREZ SANZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9893999999999999</v>
+        <v>1.7415</v>
       </c>
       <c r="E16" t="n">
-        <v>2.7495</v>
+        <v>1.2709</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.7601</v>
+        <v>0.4706</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.1826</v>
+        <v>2.5374</v>
       </c>
       <c r="H16" t="n">
-        <v>0.1376</v>
+        <v>0.3696</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.3202</v>
+        <v>2.1678</v>
       </c>
       <c r="J16" t="n">
-        <v>0.6926</v>
+        <v>2.1772</v>
       </c>
       <c r="K16" t="n">
-        <v>0.6519</v>
+        <v>1.0711</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0407</v>
+        <v>1.1061</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.8752</v>
+        <v>0.3602</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.5143</v>
+        <v>-0.7015</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.3609</v>
+        <v>1.0617</v>
       </c>
       <c r="P16" t="n">
-        <v>1.5441</v>
+        <v>1.3511</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-1.9301</v>
       </c>
       <c r="R16" t="n">
-        <v>1.5441</v>
+        <v>3.2811</v>
       </c>
       <c r="S16" t="n">
-        <v>0.628</v>
+        <v>-0.5909</v>
       </c>
       <c r="T16" t="n">
-        <v>0.8289</v>
+        <v>-0.4901</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.201</v>
+        <v>-0.1008</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>-1.5561</v>
       </c>
       <c r="W16" t="n">
-        <v>1.228</v>
+        <v>1.5138</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.228</v>
+        <v>-3.0699</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>U. PEREZ SANZ</t>
+          <t>J. ELOSEGUI OLANO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.8273</v>
+        <v>0.4194</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1693</v>
+        <v>-0.9831</v>
       </c>
       <c r="F17" t="n">
-        <v>0.658</v>
+        <v>1.4025</v>
       </c>
       <c r="G17" t="n">
-        <v>2.5374</v>
+        <v>-0.5014</v>
       </c>
       <c r="H17" t="n">
-        <v>0.3696</v>
+        <v>-0.6592</v>
       </c>
       <c r="I17" t="n">
-        <v>2.1678</v>
+        <v>0.1578</v>
       </c>
       <c r="J17" t="n">
-        <v>2.1772</v>
+        <v>-1.2488</v>
       </c>
       <c r="K17" t="n">
-        <v>1.0711</v>
+        <v>-0.6055</v>
       </c>
       <c r="L17" t="n">
-        <v>1.1061</v>
+        <v>-0.6433</v>
       </c>
       <c r="M17" t="n">
-        <v>0.3602</v>
+        <v>0.7474</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.7015</v>
+        <v>-0.0537</v>
       </c>
       <c r="O17" t="n">
-        <v>1.0617</v>
+        <v>0.8011</v>
       </c>
       <c r="P17" t="n">
-        <v>1.3511</v>
+        <v>1.158</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.9301</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>3.2811</v>
+        <v>1.158</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.5051</v>
+        <v>-0.2373</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.5916</v>
+        <v>0.2657</v>
       </c>
       <c r="U17" t="n">
-        <v>0.08649999999999999</v>
+        <v>-0.503</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.5561</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.5138</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-3.0699</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. ELOSEGUI OLANO</t>
+          <t>J. URTXULUTEGI NAVARRI</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4729</v>
+        <v>0.342</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.9831</v>
+        <v>2.0485</v>
       </c>
       <c r="F18" t="n">
-        <v>1.456</v>
+        <v>-1.7065</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.5014</v>
+        <v>-1.1826</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6592</v>
+        <v>0.1376</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1578</v>
+        <v>-1.3202</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.2488</v>
+        <v>0.6926</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.6055</v>
+        <v>0.6519</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.6433</v>
+        <v>0.0407</v>
       </c>
       <c r="M18" t="n">
-        <v>0.7474</v>
+        <v>-1.8752</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.0537</v>
+        <v>-0.5143</v>
       </c>
       <c r="O18" t="n">
-        <v>0.8011</v>
+        <v>-1.3609</v>
       </c>
       <c r="P18" t="n">
-        <v>1.158</v>
+        <v>1.5441</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.158</v>
+        <v>1.5441</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.1838</v>
+        <v>-0.0195</v>
       </c>
       <c r="T18" t="n">
-        <v>0.2657</v>
+        <v>0.1279</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4495</v>
+        <v>-0.1474</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.228</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-1.228</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1008</v>
+        <v>0.1543</v>
       </c>
       <c r="E19" t="n">
         <v>-0.2551</v>
       </c>
       <c r="F19" t="n">
-        <v>0.3559</v>
+        <v>0.4094</v>
       </c>
       <c r="G19" t="n">
         <v>-1.0322</v>
@@ -1936,13 +1936,13 @@
         <v>1.5441</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.4111</v>
+        <v>-0.3576</v>
       </c>
       <c r="T19" t="n">
         <v>-0.2102</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.201</v>
+        <v>-0.1474</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.5436</v>
+        <v>-0.2363</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.6814</v>
+        <v>-0.4812</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1378</v>
+        <v>0.2449</v>
       </c>
       <c r="G20" t="n">
         <v>1.17</v>
@@ -2014,13 +2014,13 @@
         <v>1.5441</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.0417</v>
+        <v>-0.7344000000000001</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4019</v>
+        <v>-0.2016</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.6399</v>
+        <v>-0.5328000000000001</v>
       </c>
       <c r="V20" t="n">
         <v>-0.2859</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. ARMENDARIZ LOPEZ</t>
+          <t>O. FERNANDEZ GOENAGA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.3151</v>
+        <v>-1.7237</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.953</v>
+        <v>-0.3396</v>
       </c>
       <c r="F21" t="n">
-        <v>2.638</v>
+        <v>-1.3841</v>
       </c>
       <c r="G21" t="n">
-        <v>-4.0984</v>
+        <v>0.2233</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.895</v>
+        <v>0.4968</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.2034</v>
+        <v>-0.2735</v>
       </c>
       <c r="J21" t="n">
-        <v>-4.1916</v>
+        <v>0.7038</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.9265</v>
+        <v>0.7038</v>
       </c>
       <c r="L21" t="n">
-        <v>-3.2652</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.09320000000000001</v>
+        <v>-0.4805</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.9685</v>
+        <v>-0.207</v>
       </c>
       <c r="O21" t="n">
-        <v>1.0617</v>
+        <v>-0.2735</v>
       </c>
       <c r="P21" t="n">
-        <v>1.7371</v>
+        <v>-0.579</v>
       </c>
       <c r="Q21" t="n">
         <v>-0.965</v>
       </c>
       <c r="R21" t="n">
-        <v>2.7021</v>
+        <v>0.386</v>
       </c>
       <c r="S21" t="n">
-        <v>0.4323</v>
+        <v>-0.3454</v>
       </c>
       <c r="T21" t="n">
-        <v>0.5897</v>
+        <v>-0.07829999999999999</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1574</v>
+        <v>-0.267</v>
       </c>
       <c r="V21" t="n">
-        <v>0.614</v>
+        <v>-1.0226</v>
       </c>
       <c r="W21" t="n">
-        <v>0.614</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-1.0226</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>B. ETXEBERRIA AGUIRREZABALA</t>
+          <t>A. ARMENDARIZ LOPEZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.5332</v>
+        <v>-1.8227</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.4393</v>
+        <v>-4.3536</v>
       </c>
       <c r="F22" t="n">
-        <v>1.906</v>
+        <v>2.5309</v>
       </c>
       <c r="G22" t="n">
-        <v>-3.5836</v>
+        <v>-4.0984</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.6704</v>
+        <v>-1.895</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.9132</v>
+        <v>-2.2034</v>
       </c>
       <c r="J22" t="n">
-        <v>-2.2092</v>
+        <v>-4.1916</v>
       </c>
       <c r="K22" t="n">
-        <v>-2.3963</v>
+        <v>-0.9265</v>
       </c>
       <c r="L22" t="n">
-        <v>0.1871</v>
+        <v>-3.2652</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.3744</v>
+        <v>0.09320000000000001</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.2741</v>
+        <v>-0.9685</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.1003</v>
+        <v>1.0617</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.579</v>
+        <v>1.7371</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.8951</v>
+        <v>-0.965</v>
       </c>
       <c r="R22" t="n">
-        <v>2.3161</v>
+        <v>2.7021</v>
       </c>
       <c r="S22" t="n">
-        <v>1.5243</v>
+        <v>-0.07530000000000001</v>
       </c>
       <c r="T22" t="n">
-        <v>1.0933</v>
+        <v>0.1891</v>
       </c>
       <c r="U22" t="n">
-        <v>0.4309</v>
+        <v>-0.2644</v>
       </c>
       <c r="V22" t="n">
-        <v>1.1052</v>
+        <v>0.614</v>
       </c>
       <c r="W22" t="n">
-        <v>0.5717</v>
+        <v>0.614</v>
       </c>
       <c r="X22" t="n">
-        <v>0.5334</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>O. FERNANDEZ GOENAGA</t>
+          <t>B. ETXEBERRIA AGUIRREZABALA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.8239</v>
+        <v>-2.7627</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.4397</v>
+        <v>-4.2404</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.3841</v>
+        <v>1.4777</v>
       </c>
       <c r="G23" t="n">
-        <v>0.2233</v>
+        <v>-3.5836</v>
       </c>
       <c r="H23" t="n">
-        <v>0.4968</v>
+        <v>-2.6704</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.2735</v>
+        <v>-0.9132</v>
       </c>
       <c r="J23" t="n">
-        <v>0.7038</v>
+        <v>-2.2092</v>
       </c>
       <c r="K23" t="n">
-        <v>0.7038</v>
+        <v>-2.3963</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>0.1871</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.4805</v>
+        <v>-1.3744</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.207</v>
+        <v>-0.2741</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.2735</v>
+        <v>-1.1003</v>
       </c>
       <c r="P23" t="n">
         <v>-0.579</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.965</v>
+        <v>-2.8951</v>
       </c>
       <c r="R23" t="n">
-        <v>0.386</v>
+        <v>2.3161</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.4455</v>
+        <v>0.2948</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.1785</v>
+        <v>0.2922</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.267</v>
+        <v>0.0026</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.0226</v>
+        <v>1.1052</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>0.5717</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.0226</v>
+        <v>0.5334</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.1171</v>
+        <v>-3.5559</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.7776</v>
+        <v>-2.377</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.3395</v>
+        <v>-1.1789</v>
       </c>
       <c r="G24" t="n">
         <v>-1.0129</v>
@@ -2326,13 +2326,13 @@
         <v>2.1231</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.1118</v>
+        <v>-0.5506</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.612</v>
+        <v>-0.2115</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.4997</v>
+        <v>-0.3391</v>
       </c>
       <c r="V24" t="n">
         <v>-3.1505</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-8.908799999999999</v>
+        <v>-8.4815</v>
       </c>
       <c r="E25" t="n">
-        <v>-5.9222</v>
+        <v>-5.5217</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.9866</v>
+        <v>-2.9598</v>
       </c>
       <c r="G25" t="n">
         <v>-7.5966</v>
@@ -2404,13 +2404,13 @@
         <v>1.158</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.0966</v>
+        <v>-0.6692</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.6107</v>
+        <v>-0.2102</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.4858</v>
+        <v>-0.4591</v>
       </c>
       <c r="V25" t="n">
         <v>-0.4087</v>
@@ -2440,25 +2440,25 @@
         <v>-13.4439</v>
       </c>
       <c r="E26" t="n">
-        <v>-14.8558</v>
+        <v>-14.8559</v>
       </c>
       <c r="F26" t="n">
-        <v>1.411899999999998</v>
+        <v>1.412</v>
       </c>
       <c r="G26" t="n">
         <v>-12.4891</v>
       </c>
       <c r="H26" t="n">
-        <v>-7.912299999999999</v>
+        <v>-7.9123</v>
       </c>
       <c r="I26" t="n">
-        <v>-4.576700000000001</v>
+        <v>-4.5767</v>
       </c>
       <c r="J26" t="n">
         <v>-9.354099999999999</v>
       </c>
       <c r="K26" t="n">
-        <v>-5.6057</v>
+        <v>-5.605700000000001</v>
       </c>
       <c r="L26" t="n">
         <v>-3.7484</v>
@@ -2482,13 +2482,13 @@
         <v>19.3008</v>
       </c>
       <c r="S26" t="n">
-        <v>-4.0914</v>
+        <v>-4.0915</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.5483</v>
+        <v>-0.5484</v>
       </c>
       <c r="U26" t="n">
-        <v>-3.543299999999999</v>
+        <v>-3.543</v>
       </c>
       <c r="V26" t="n">
         <v>-4.5838</v>
